--- a/diseases/d102/2020-2025.xlsx
+++ b/diseases/d102/2020-2025.xlsx
@@ -1061,9 +1061,6 @@
       <c r="O4" t="n">
         <v>162</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>2.929681142185022</v>
       </c>
@@ -1753,9 +1750,6 @@
       <c r="O8" t="n">
         <v>92</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>1.663769537537173</v>
       </c>
@@ -2445,9 +2439,6 @@
       <c r="O12" t="n">
         <v>45</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.813800317273617</v>
       </c>
@@ -3137,9 +3128,6 @@
       <c r="O16" t="n">
         <v>22</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.3978579328893239</v>
       </c>
@@ -3829,9 +3817,6 @@
       <c r="O20" t="n">
         <v>48</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.8680536717585249</v>
       </c>
@@ -4521,9 +4506,6 @@
       <c r="O24" t="n">
         <v>95</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>1.71802289202208</v>
       </c>
@@ -5213,9 +5195,6 @@
       <c r="O28" t="n">
         <v>81</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>1.464840571092511</v>
       </c>
@@ -5905,9 +5884,6 @@
       <c r="O32" t="n">
         <v>103</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>1.862698503981835</v>
       </c>
@@ -6597,9 +6573,6 @@
       <c r="O36" t="n">
         <v>113</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>2.043543018931527</v>
       </c>
@@ -7289,9 +7262,6 @@
       <c r="O40" t="n">
         <v>134</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>2.423316500325882</v>
       </c>
@@ -7981,9 +7951,6 @@
       <c r="O44" t="n">
         <v>122</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>2.206303082386251</v>
       </c>
@@ -8673,9 +8640,6 @@
       <c r="O48" t="n">
         <v>149</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>2.694583272750421</v>
       </c>
@@ -9513,9 +9477,6 @@
       <c r="O53" t="n">
         <v>131</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>2.364162188744964</v>
       </c>
@@ -10205,9 +10166,6 @@
       <c r="O57" t="n">
         <v>61</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>1.100869416133151</v>
       </c>
@@ -10897,9 +10855,6 @@
       <c r="O61" t="n">
         <v>25</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.4511759902185046</v>
       </c>
@@ -11589,9 +11544,6 @@
       <c r="O65" t="n">
         <v>36</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.6496934259146465</v>
       </c>
@@ -12281,9 +12233,6 @@
       <c r="O69" t="n">
         <v>86</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>1.552045406351656</v>
       </c>
@@ -12973,9 +12922,6 @@
       <c r="O73" t="n">
         <v>107</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>1.9310332381352</v>
       </c>
@@ -13665,9 +13611,6 @@
       <c r="O77" t="n">
         <v>110</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>1.98517435696142</v>
       </c>
@@ -14357,9 +14300,6 @@
       <c r="O81" t="n">
         <v>134</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>2.418303307571184</v>
       </c>
@@ -15049,9 +14989,6 @@
       <c r="O85" t="n">
         <v>107</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>1.9310332381352</v>
       </c>
@@ -15741,9 +15678,6 @@
       <c r="O89" t="n">
         <v>186</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>3.356749367225674</v>
       </c>
@@ -16433,9 +16367,6 @@
       <c r="O93" t="n">
         <v>219</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>3.9523016743141</v>
       </c>
@@ -17125,9 +17056,6 @@
       <c r="O97" t="n">
         <v>226</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>4.078630951575281</v>
       </c>
@@ -17965,9 +17893,6 @@
       <c r="O102" t="n">
         <v>130</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>2.3342255461594</v>
       </c>
@@ -19249,9 +19174,6 @@
       <c r="O110" t="n">
         <v>98</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>1.759646950181701</v>
       </c>
@@ -20533,9 +20455,6 @@
       <c r="O118" t="n">
         <v>88</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>1.580091138938671</v>
       </c>
@@ -21817,9 +21736,6 @@
       <c r="O126" t="n">
         <v>59</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>1.059379286333882</v>
       </c>
@@ -23249,9 +23165,6 @@
       <c r="O135" t="n">
         <v>57</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>1.023468124085275</v>
       </c>
@@ -24533,9 +24446,6 @@
       <c r="O143" t="n">
         <v>102</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>1.831469274678914</v>
       </c>
@@ -25817,9 +25727,6 @@
       <c r="O151" t="n">
         <v>94</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>1.687824625684489</v>
       </c>
@@ -27249,9 +27156,6 @@
       <c r="O160" t="n">
         <v>125</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>2.244447640537885</v>
       </c>
@@ -28533,9 +28437,6 @@
       <c r="O168" t="n">
         <v>111</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>1.993069504797641</v>
       </c>
@@ -29817,9 +29718,6 @@
       <c r="O176" t="n">
         <v>122</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>2.190580897164975</v>
       </c>
@@ -31249,9 +31147,6 @@
       <c r="O185" t="n">
         <v>161</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>2.890848561012795</v>
       </c>
@@ -32533,9 +32428,6 @@
       <c r="O193" t="n">
         <v>152</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>2.729248330894067</v>
       </c>
@@ -34113,9 +34005,6 @@
       <c r="O203" t="n">
         <v>94</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>1.678216156204789</v>
       </c>
@@ -35397,9 +35286,6 @@
       <c r="O211" t="n">
         <v>85</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>1.517535885929862</v>
       </c>
@@ -36681,9 +36567,6 @@
       <c r="O219" t="n">
         <v>83</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="R219" t="n">
         <v>1.481829159202101</v>
       </c>
@@ -37965,9 +37848,6 @@
       <c r="O227" t="n">
         <v>43</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>0.7676946246468717</v>
       </c>
@@ -39397,9 +39277,6 @@
       <c r="O236" t="n">
         <v>53</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0.9462282582856789</v>
       </c>
@@ -40681,9 +40558,6 @@
       <c r="O244" t="n">
         <v>62</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>1.106908528560606</v>
       </c>
@@ -41965,9 +41839,6 @@
       <c r="O252" t="n">
         <v>68</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>1.21402870874389</v>
       </c>
@@ -43397,9 +43268,6 @@
       <c r="O261" t="n">
         <v>79</v>
       </c>
-      <c r="Q261" t="n">
-        <v>0</v>
-      </c>
       <c r="R261" t="n">
         <v>1.410415705746578</v>
       </c>
@@ -44681,9 +44549,6 @@
       <c r="O269" t="n">
         <v>49</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="R269" t="n">
         <v>0.8748148048301561</v>
       </c>
@@ -46113,9 +45978,6 @@
       <c r="O278" t="n">
         <v>56</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0.9997883483773211</v>
       </c>
@@ -47397,9 +47259,6 @@
       <c r="O286" t="n">
         <v>81</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>1.44612243247434</v>
       </c>
@@ -48681,9 +48540,6 @@
       <c r="O294" t="n">
         <v>59</v>
       </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
       <c r="R294" t="n">
         <v>1.053348438468963</v>
       </c>
@@ -50113,9 +49969,6 @@
       <c r="O303" t="n">
         <v>0</v>
       </c>
-      <c r="Q303" t="n">
-        <v>0</v>
-      </c>
       <c r="R303" t="n">
         <v>0</v>
       </c>
@@ -50261,9 +50114,6 @@
       <c r="O304" t="n">
         <v>64</v>
       </c>
-      <c r="Q304" t="n">
-        <v>0</v>
-      </c>
       <c r="R304" t="n">
         <v>1.139335274416467</v>
       </c>
@@ -51545,9 +51395,6 @@
       <c r="O312" t="n">
         <v>41</v>
       </c>
-      <c r="Q312" t="n">
-        <v>0</v>
-      </c>
       <c r="R312" t="n">
         <v>0.7298866601730489</v>
       </c>
@@ -52829,9 +52676,6 @@
       <c r="O320" t="n">
         <v>23</v>
       </c>
-      <c r="Q320" t="n">
-        <v>0</v>
-      </c>
       <c r="R320" t="n">
         <v>0.4094486142434178</v>
       </c>
@@ -54261,9 +54105,6 @@
       <c r="O329" t="n">
         <v>28</v>
       </c>
-      <c r="Q329" t="n">
-        <v>0</v>
-      </c>
       <c r="R329" t="n">
         <v>0.4984591825572042</v>
       </c>
@@ -55545,9 +55386,6 @@
       <c r="O337" t="n">
         <v>37</v>
       </c>
-      <c r="Q337" t="n">
-        <v>0</v>
-      </c>
       <c r="R337" t="n">
         <v>0.6586782055220198</v>
       </c>
@@ -56829,9 +56667,6 @@
       <c r="O345" t="n">
         <v>39</v>
       </c>
-      <c r="Q345" t="n">
-        <v>0</v>
-      </c>
       <c r="R345" t="n">
         <v>0.6942824328475344</v>
       </c>
@@ -58261,9 +58096,6 @@
       <c r="O354" t="n">
         <v>45</v>
       </c>
-      <c r="Q354" t="n">
-        <v>0</v>
-      </c>
       <c r="R354" t="n">
         <v>0.8010951148240782</v>
       </c>
@@ -59545,9 +59377,6 @@
       <c r="O362" t="n">
         <v>34</v>
       </c>
-      <c r="Q362" t="n">
-        <v>0</v>
-      </c>
       <c r="R362" t="n">
         <v>0.6052718645337479</v>
       </c>
@@ -60977,9 +60806,6 @@
       <c r="O371" t="n">
         <v>55</v>
       </c>
-      <c r="Q371" t="n">
-        <v>0</v>
-      </c>
       <c r="R371" t="n">
         <v>0.9791162514516512</v>
       </c>
@@ -62261,9 +62087,6 @@
       <c r="O379" t="n">
         <v>52</v>
       </c>
-      <c r="Q379" t="n">
-        <v>0</v>
-      </c>
       <c r="R379" t="n">
         <v>0.9257099104633792</v>
       </c>
@@ -63545,9 +63368,6 @@
       <c r="O387" t="n">
         <v>82</v>
       </c>
-      <c r="Q387" t="n">
-        <v>0</v>
-      </c>
       <c r="R387" t="n">
         <v>1.459773320346098</v>
       </c>
@@ -64977,9 +64797,6 @@
       <c r="O396" t="n">
         <v>86</v>
       </c>
-      <c r="Q396" t="n">
-        <v>0</v>
-      </c>
       <c r="R396" t="n">
         <v>1.530981774997127</v>
       </c>
@@ -66261,9 +66078,6 @@
       <c r="O404" t="n">
         <v>2</v>
       </c>
-      <c r="Q404" t="n">
-        <v>0</v>
-      </c>
       <c r="R404" t="n">
         <v>0.02230299002247862</v>
       </c>
@@ -66409,9 +66223,6 @@
       <c r="O405" t="n">
         <v>80</v>
       </c>
-      <c r="Q405" t="n">
-        <v>0</v>
-      </c>
       <c r="R405" t="n">
         <v>1.422644716088573</v>
       </c>
@@ -67693,9 +67504,6 @@
       <c r="O413" t="n">
         <v>49</v>
       </c>
-      <c r="Q413" t="n">
-        <v>0</v>
-      </c>
       <c r="R413" t="n">
         <v>0.8713698886042514</v>
       </c>
@@ -68977,9 +68785,6 @@
       <c r="O421" t="n">
         <v>25</v>
       </c>
-      <c r="Q421" t="n">
-        <v>0</v>
-      </c>
       <c r="R421" t="n">
         <v>0.4445764737776792</v>
       </c>
@@ -70409,9 +70214,6 @@
       <c r="O430" t="n">
         <v>23</v>
       </c>
-      <c r="Q430" t="n">
-        <v>0</v>
-      </c>
       <c r="R430" t="n">
         <v>0.4090103558754649</v>
       </c>
@@ -71693,9 +71495,6 @@
       <c r="O438" t="n">
         <v>33</v>
       </c>
-      <c r="Q438" t="n">
-        <v>0</v>
-      </c>
       <c r="R438" t="n">
         <v>0.5868409453865366</v>
       </c>
@@ -73125,9 +72924,6 @@
       <c r="O447" t="n">
         <v>73</v>
       </c>
-      <c r="Q447" t="n">
-        <v>0</v>
-      </c>
       <c r="R447" t="n">
         <v>1.298163303430823</v>
       </c>
@@ -74409,9 +74205,6 @@
       <c r="O455" t="n">
         <v>105</v>
       </c>
-      <c r="Q455" t="n">
-        <v>0</v>
-      </c>
       <c r="R455" t="n">
         <v>1.867221189866253</v>
       </c>
@@ -75693,9 +75486,6 @@
       <c r="O463" t="n">
         <v>128</v>
       </c>
-      <c r="Q463" t="n">
-        <v>0</v>
-      </c>
       <c r="R463" t="n">
         <v>2.276231545741718</v>
       </c>
@@ -77125,9 +76915,6 @@
       <c r="O472" t="n">
         <v>111</v>
       </c>
-      <c r="Q472" t="n">
-        <v>0</v>
-      </c>
       <c r="R472" t="n">
         <v>1.973919543572896</v>
       </c>
@@ -78409,9 +78196,6 @@
       <c r="O480" t="n">
         <v>95</v>
       </c>
-      <c r="Q480" t="n">
-        <v>0</v>
-      </c>
       <c r="R480" t="n">
         <v>1.689390600355181</v>
       </c>
@@ -79693,9 +79477,6 @@
       <c r="O488" t="n">
         <v>146</v>
       </c>
-      <c r="Q488" t="n">
-        <v>0</v>
-      </c>
       <c r="R488" t="n">
         <v>2.596326606861647</v>
       </c>
@@ -81124,9 +80905,6 @@
       </c>
       <c r="O497" t="n">
         <v>146</v>
-      </c>
-      <c r="Q497" t="n">
-        <v>0</v>
       </c>
       <c r="R497" t="n">
         <v>2.596326606861647</v>
